--- a/Convert_from_xlsx_to_Json/table_normalization/education-table07.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table07.xlsx
@@ -459,9 +459,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -506,6 +503,50 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -515,52 +556,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1141,7 +1141,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1149,78 +1149,78 @@
       <c r="A2" s="8"/>
     </row>
     <row r="3" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="32" t="s">
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="34"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="49"/>
     </row>
     <row r="4" spans="1:17" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="43" t="s">
+      <c r="J4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="43" t="s">
+      <c r="K4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="43" t="s">
+      <c r="M4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="43" t="s">
+      <c r="N4" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="43" t="s">
+      <c r="O4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="43" t="s">
+      <c r="P4" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="44" t="s">
+      <c r="Q4" s="32" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       <c r="H5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="22">
         <v>819500</v>
       </c>
       <c r="J5" s="10">
@@ -1273,7 +1273,7 @@
       <c r="P5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="22">
         <v>476100</v>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       <c r="H6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="23">
         <v>675300</v>
       </c>
       <c r="J6" s="12">
@@ -1326,7 +1326,7 @@
       <c r="P6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="23">
         <v>369800</v>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       <c r="H7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="22">
         <v>227000</v>
       </c>
       <c r="J7" s="10">
@@ -1379,96 +1379,96 @@
       <c r="P7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="22">
         <v>156400</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>702230</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>39820</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>30150</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>204990</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <v>990</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>315610</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <v>4000</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <v>1297800</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <v>461690</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>29910</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="16">
         <v>19310</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="16">
         <v>143500</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="16">
         <v>640</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <v>164210</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="16">
         <v>1830</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="24">
         <v>821100</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
       <c r="P9" s="10"/>
-      <c r="Q9" s="31"/>
+      <c r="Q9" s="30"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
@@ -1479,17 +1479,17 @@
       <c r="Q10"/>
     </row>
     <row r="11" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
@@ -1500,44 +1500,44 @@
       <c r="Q11"/>
     </row>
     <row r="12" spans="1:17" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
       <c r="P12"/>
       <c r="Q12"/>
     </row>
     <row r="13" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
       <c r="P13"/>
       <c r="Q13"/>
     </row>
@@ -1903,225 +1903,225 @@
       <c r="Q32"/>
     </row>
     <row r="33" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P34" s="10"/>
-      <c r="Q34" s="31"/>
+      <c r="Q34" s="30"/>
     </row>
     <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P35" s="10"/>
-      <c r="Q35" s="31"/>
+      <c r="Q35" s="30"/>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="35"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+      <c r="O38" s="45"/>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="28"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="27"/>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="27"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="26"/>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="27"/>
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="26"/>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="38"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="27"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="26"/>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="28"/>
+      <c r="A43" s="39"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="27"/>
     </row>
     <row r="44" spans="1:17" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
     </row>
     <row r="45" spans="1:17" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="41"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
+      <c r="A45" s="43"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
     </row>
     <row r="46" spans="1:17" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="38"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="30"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="43"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="43"/>
+      <c r="P46" s="29"/>
     </row>
     <row r="47" spans="1:17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="28"/>
+      <c r="A48" s="39"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A44:O44"/>
     <mergeCell ref="A45:O45"/>
     <mergeCell ref="A46:O46"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.39370078740157499" right="0.47244094488188998" top="0.98425196850393704" bottom="0.98425196850393704" header="0.47244094488188998" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="52" orientation="landscape"/>
